--- a/Enter/enter_test_info.xlsx
+++ b/Enter/enter_test_info.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="26925" windowHeight="7725"/>
   </bookViews>
   <sheets>
-    <sheet name="豚" sheetId="8" r:id="rId1"/>
-    <sheet name="潜" sheetId="7" r:id="rId2"/>
-    <sheet name="红白" sheetId="5" r:id="rId3"/>
-    <sheet name="篮球投率" sheetId="10" r:id="rId4"/>
-    <sheet name="跳" sheetId="9" r:id="rId5"/>
-    <sheet name="矿" sheetId="12" r:id="rId6"/>
+    <sheet name="矿" sheetId="12" r:id="rId1"/>
+    <sheet name="豚" sheetId="8" r:id="rId2"/>
+    <sheet name="潜" sheetId="7" r:id="rId3"/>
+    <sheet name="红白" sheetId="5" r:id="rId4"/>
+    <sheet name="篮球投率" sheetId="10" r:id="rId5"/>
+    <sheet name="跳" sheetId="9" r:id="rId6"/>
     <sheet name="梯" sheetId="11" r:id="rId7"/>
     <sheet name="橄" sheetId="6" r:id="rId8"/>
   </sheets>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="52">
   <si>
     <t>小丑类型</t>
   </si>
@@ -95,13 +95,16 @@
     <t>曾</t>
   </si>
   <si>
-    <t>非永动</t>
+    <t>永动</t>
   </si>
   <si>
-    <t>炮</t>
+    <t>卡</t>
   </si>
   <si>
     <t>被炸植物列数</t>
+  </si>
+  <si>
+    <t>非永动</t>
   </si>
   <si>
     <t>被炸植物类型</t>
@@ -119,13 +122,16 @@
     <t>已有伤害</t>
   </si>
   <si>
+    <t>喷</t>
+  </si>
+  <si>
     <t>冰瓜额外溅射次数</t>
   </si>
   <si>
     <t>僵尸类型</t>
   </si>
   <si>
-    <t>豚</t>
+    <t>矿</t>
   </si>
   <si>
     <t>测试次数</t>
@@ -152,13 +158,22 @@
     <t>锁植物攻击间隔</t>
   </si>
   <si>
-    <t>潜</t>
+    <t>（矿工）植物防御左限</t>
   </si>
   <si>
-    <t>永动</t>
+    <t>（矿工）植物列</t>
   </si>
   <si>
-    <t>喷</t>
+    <t>（矿工）植物防御左限偏移</t>
+  </si>
+  <si>
+    <t>炮</t>
+  </si>
+  <si>
+    <t>豚</t>
+  </si>
+  <si>
+    <t>潜</t>
   </si>
   <si>
     <t>红</t>
@@ -171,9 +186,6 @@
   </si>
   <si>
     <t>跳</t>
-  </si>
-  <si>
-    <t>矿</t>
   </si>
   <si>
     <t>梯</t>
@@ -368,13 +380,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,7 +772,7 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -834,22 +846,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1377,23 +1389,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet3"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="2" max="2" width="8.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -1409,18 +1421,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -1443,10 +1455,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -1463,32 +1475,32 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="7">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>96</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6">
-        <v>95</v>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1975</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8">
+        <v>6000</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
+      <c r="O3" s="8">
+        <v>-100</v>
+      </c>
+      <c r="P3" s="8">
         <v>900</v>
       </c>
     </row>
@@ -1499,382 +1511,401 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="7">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
+        <v>3</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>5</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>8</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>6</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="5">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
+        <v>10000000</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
         <v>5000</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>140</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1929,23 +1960,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet23"/>
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -1961,18 +1992,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -1995,10 +2026,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -2015,26 +2046,34 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="6">
-        <v>3000</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
+        <v>96</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8">
+        <v>95</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="8">
+        <v>100</v>
+      </c>
+      <c r="P3" s="8">
+        <v>900</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3" t="s">
@@ -2043,382 +2082,401 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
-        <v>2</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>5</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="5">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="7">
         <v>9</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
         <v>1000000</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
-        <v>6000</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2473,23 +2531,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet7"/>
+  <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -2505,18 +2563,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -2539,10 +2597,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -2559,26 +2617,26 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>40</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8">
+        <v>3000</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8"/>
       <c r="N3" s="9"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3" t="s">
@@ -2587,382 +2645,401 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="7">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>6</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="G5" s="7">
+        <v>2</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>6</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="7">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
         <v>1000000</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:16">
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3017,23 +3094,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet4"/>
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="2" max="2" width="8.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -3049,18 +3126,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -3083,10 +3160,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -3103,26 +3180,26 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>1</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
+        <v>40</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8"/>
       <c r="N3" s="9"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3" t="s">
@@ -3131,382 +3208,401 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
-        <v>2</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
         <v>6</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
         <v>1000000</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
-        <v>3000</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:16">
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3561,23 +3657,23 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet2"/>
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -3593,18 +3689,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -3627,10 +3723,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -3647,32 +3743,26 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
         <v>1</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3" t="s">
@@ -3681,382 +3771,401 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="7">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>5</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
         <v>6</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
-        <v>10000000</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
+        <v>3000</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4111,23 +4220,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -4143,18 +4252,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -4177,10 +4286,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -4197,26 +4306,32 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>1617</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8">
+        <v>1039</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="8">
+        <v>100</v>
+      </c>
+      <c r="P3" s="8">
+        <v>900</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3" t="s">
@@ -4225,382 +4340,401 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="7">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="I4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>6</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
-        <v>6</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
+        <v>5</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
         <v>6</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
+        <v>10000000</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
         <v>5000</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4657,21 +4791,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -4687,18 +4821,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -4721,10 +4855,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -4741,26 +4875,26 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="7">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7">
         <v>1</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="8">
         <v>783</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8"/>
       <c r="N3" s="9"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3" t="s">
@@ -4769,385 +4903,404 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="7">
         <v>3</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
         <f>I3+2501</f>
         <v>3284</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
         <v>4</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="F5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
         <v>6</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
         <v>10000000</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
         <v>5000</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5204,21 +5357,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.23076923076923" style="1"/>
+    <col min="3" max="3" width="9.23333333333333" style="1"/>
     <col min="4" max="6" width="8.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.23076923076923" style="1"/>
+    <col min="8" max="8" width="9.23333333333333" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.23076923076923" style="1"/>
+    <col min="10" max="10" width="9.23333333333333" style="1"/>
     <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.23076923076923" style="1"/>
+    <col min="12" max="12" width="9.23333333333333" style="1"/>
     <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
     <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
@@ -5234,18 +5387,18 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="3" t="s">
@@ -5268,10 +5421,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -5288,26 +5441,26 @@
       <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
+      <c r="F3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
         <v>830</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8"/>
       <c r="N3" s="9"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="3" t="s">
@@ -5316,385 +5469,404 @@
       <c r="B4" s="3">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="7">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="8">
         <f>I3+2501</f>
         <v>3331</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="K4" s="8"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7">
         <v>6</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7">
         <v>1</v>
       </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="E7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="M7" s="8"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
         <v>6</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="M8" s="8"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6">
+        <v>32</v>
+      </c>
+      <c r="B10" s="8">
         <v>10000000</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6">
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
         <v>5000</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:16">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8">
+        <f>-40+80*B18+B19</f>
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:16">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:16">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:16">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:16">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:16">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:16">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:16">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:16">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
